--- a/ksoft_old/docs/records/Business_Unit_Records.xlsx
+++ b/ksoft_old/docs/records/Business_Unit_Records.xlsx
@@ -1498,13 +1498,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EEE352C-1662-4862-9033-524A5E3492A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEC45B21-3548-45B0-81E3-6D4C5D942CE1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75242278-DC36-42BE-8840-3566770894B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3709A84-8E38-4724-9BBB-5FD64FE37B15}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{127C2978-233A-4F56-A75C-A4516F10DD6F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD24D330-C5F7-4361-BE48-B7E8B9709804}"/>
 </file>
--- a/ksoft_old/docs/records/Business_Unit_Records.xlsx
+++ b/ksoft_old/docs/records/Business_Unit_Records.xlsx
@@ -1498,13 +1498,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEC45B21-3548-45B0-81E3-6D4C5D942CE1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2719CF93-7CC9-42A9-B499-6474A21E8DE9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3709A84-8E38-4724-9BBB-5FD64FE37B15}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{032B3A78-1C23-4B65-81EE-D57BF295ECFF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD24D330-C5F7-4361-BE48-B7E8B9709804}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D209290-0440-440C-BEF2-7CB02967998D}"/>
 </file>
--- a/ksoft_old/docs/records/Business_Unit_Records.xlsx
+++ b/ksoft_old/docs/records/Business_Unit_Records.xlsx
@@ -1498,13 +1498,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2719CF93-7CC9-42A9-B499-6474A21E8DE9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EEE352C-1662-4862-9033-524A5E3492A1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{032B3A78-1C23-4B65-81EE-D57BF295ECFF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75242278-DC36-42BE-8840-3566770894B3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D209290-0440-440C-BEF2-7CB02967998D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{127C2978-233A-4F56-A75C-A4516F10DD6F}"/>
 </file>